--- a/content/shop.xlsx
+++ b/content/shop.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="25">
   <si>
     <t>kind</t>
   </si>
@@ -22,6 +22,9 @@
     <t>stat</t>
   </si>
   <si>
+    <t>statName</t>
+  </si>
+  <si>
     <t>value</t>
   </si>
   <si>
@@ -34,6 +37,9 @@
     <t>dance</t>
   </si>
   <si>
+    <t>舞蹈</t>
+  </si>
+  <si>
     <t>旧卫衣</t>
   </si>
   <si>
@@ -43,12 +49,18 @@
     <t>acting</t>
   </si>
   <si>
+    <t>演技</t>
+  </si>
+  <si>
     <t>针织开衫</t>
   </si>
   <si>
     <t>vocal</t>
   </si>
   <si>
+    <t>演唱</t>
+  </si>
+  <si>
     <t>运动外套</t>
   </si>
   <si>
@@ -56,6 +68,9 @@
   </si>
   <si>
     <t>talk</t>
+  </si>
+  <si>
+    <t>口才</t>
   </si>
   <si>
     <t>rare</t>
@@ -456,14 +471,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -476,144 +492,177 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3">
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4">
+      <c r="E6">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
         <v>11</v>
       </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="D9" t="s">
         <v>12</v>
       </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="E9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
         <v>14</v>
       </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="D11" t="s">
         <v>15</v>
       </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11">
+      <c r="E11">
         <v>5</v>
       </c>
     </row>
